--- a/data/pubs.xlsx
+++ b/data/pubs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jimwright/Desktop/Resume/wright_cv/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB6AD804-F712-C04D-B19C-73D2AB31DDB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A2F1346-8D87-9549-BF95-8FD6024A4348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16320" xr2:uid="{9F01FDA3-1E1B-6547-B661-3F940585A8E2}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="16160" xr2:uid="{9F01FDA3-1E1B-6547-B661-3F940585A8E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="109">
   <si>
     <t>type</t>
   </si>
@@ -313,16 +313,71 @@
   </si>
   <si>
     <t>Parent/Guardian Survey on Childhood Immunization and Vaccination: Spring 2025 - Prepared for the Kern County Immunization Coalition</t>
+  </si>
+  <si>
+    <t>Childcare Strategic Plan - Prepared for the Plumas County Office of Education and Plumas County LPC</t>
+  </si>
+  <si>
+    <t>Childcare Needs Assessment - Prepared for the Plumas County Office of Education and Plumas County LPC</t>
+  </si>
+  <si>
+    <t>First 5 Plumas Strategic Plan 2026-2031 - Prepared for First 5 Plumas</t>
+  </si>
+  <si>
+    <t>First 5 Kern Annual Evaluation Report, FY 2023-2024 - Prepared for First 5 Kern</t>
+  </si>
+  <si>
+    <t>Hess, C., Handman, R., &amp; Wright, J.</t>
+  </si>
+  <si>
+    <t>First 5 Kern Annual Evaluation Report, FY 2024-2025 - Prepared for First 5 Kern</t>
+  </si>
+  <si>
+    <t>First 5 Lake Annual Evaluation Report, FY 2024-2025 - Prepared for First 5 Lake</t>
+  </si>
+  <si>
+    <t>First 5 Yuba Annual Evaluation Report, FY 2024-2025 - Prepared for First 5 Yuba</t>
+  </si>
+  <si>
+    <t>First 5 Sutter Annual Evaluation Report, FY 2024-2025 - Prepared for First 5 Sutter</t>
+  </si>
+  <si>
+    <t>First 5 Siskiyou Annual Evaluation Report, FY 2024-2025 - Prepared for First 5 Siskiyou</t>
+  </si>
+  <si>
+    <t>Do Treatment Ingredients Targeting Working Alliance Improve Cognitive Rehabilitation Session Performance in Patients With Acquired Brain Injury? </t>
+  </si>
+  <si>
+    <t>1,023-1,040</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/40299720/</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1044/2024_ajslp-24-00347</t>
+  </si>
+  <si>
+    <t>Rothbart, A., Sohlberg, M.M., Shune, S., Seeley, J., Berkman, E., &amp; Wright, J.</t>
+  </si>
+  <si>
+    <t>Hess, C. &amp; Wright, J.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -348,12 +403,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -670,7 +728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AD3C43B-6729-8048-9A95-5F6194EDFE7F}">
-  <dimension ref="A1:W23"/>
+  <dimension ref="A1:W33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="20.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="8" width="20.83203125" style="1"/>
@@ -749,147 +807,167 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="119" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:23" ht="136" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>54</v>
+        <v>107</v>
       </c>
       <c r="D2" s="1">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>61</v>
+        <v>103</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>58</v>
+        <v>17</v>
+      </c>
+      <c r="G2" s="1">
+        <v>34</v>
+      </c>
+      <c r="H2" s="1">
+        <v>3</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>59</v>
+        <v>106</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" ht="102" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" ht="119" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="D3" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>17</v>
+        <v>58</v>
+      </c>
+      <c r="G3" s="1">
+        <v>33</v>
+      </c>
+      <c r="H3" s="1">
+        <v>7</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" ht="170" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="102" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" s="1">
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="1">
+        <v>2021</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="1">
+        <v>30</v>
+      </c>
+      <c r="H4" s="1">
+        <v>4</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="170" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D5" s="1">
         <v>2020</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G5" s="1">
         <v>40</v>
       </c>
-      <c r="H4" s="1">
+      <c r="H5" s="1">
         <v>1</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J5" t="s">
         <v>46</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="85" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="1">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="J5"/>
-      <c r="P5" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q5" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="R5" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="S5" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" ht="119" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" ht="85" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B6" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="J6"/>
       <c r="P6" s="1" t="s">
@@ -905,22 +983,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="136" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" ht="119" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>37</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="J7"/>
       <c r="P7" s="1" t="s">
         <v>47</v>
       </c>
@@ -934,12 +1013,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="119" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" ht="136" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B8" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>14</v>
@@ -948,19 +1027,19 @@
         <v>34</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="Q8" s="1" t="b">
         <v>0</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="S8" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="119" x14ac:dyDescent="0.2">
@@ -968,123 +1047,132 @@
         <v>26</v>
       </c>
       <c r="B9" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="Q9" s="1" t="b">
         <v>0</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="S9" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="136" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" ht="119" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B10" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q10" s="1" t="b">
         <v>0</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S10" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="51" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" ht="136" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B11" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="Q11" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="S11" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="119" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:23" ht="51" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="B12" s="1">
+        <v>7</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q12" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D12" s="1">
+      <c r="R12" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="S12" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" ht="68" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" s="1">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D13" s="1">
         <v>2025</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" ht="136" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B13" s="1">
-        <v>2</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D13" s="1">
-        <v>2024</v>
-      </c>
       <c r="E13" s="1" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>85</v>
@@ -1095,202 +1183,405 @@
         <v>90</v>
       </c>
       <c r="B14" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D14" s="1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="102" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" ht="68" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>90</v>
       </c>
       <c r="B15" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="D15" s="1">
-        <v>2024</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>88</v>
+        <v>2025</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>100</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="102" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" ht="68" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>90</v>
       </c>
       <c r="B16" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D16" s="1">
-        <v>2024</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>89</v>
+        <v>2025</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>101</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>90</v>
       </c>
       <c r="B17" s="1">
+        <v>5</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" s="1">
+        <v>2025</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" s="1">
         <v>6</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C18" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D18" s="1">
+        <v>2025</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" s="1">
+        <v>7</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D19" s="1">
+        <v>2025</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" s="1">
+        <v>8</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D20" s="1">
+        <v>2025</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="119" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B21" s="1">
+        <v>9</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" s="1">
+        <v>2025</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B22" s="1">
+        <v>10</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" s="1">
+        <v>2024</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="136" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B23" s="1">
+        <v>11</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D23" s="1">
+        <v>2024</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B24" s="1">
+        <v>12</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D24" s="1">
+        <v>2024</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="102" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B25" s="1">
+        <v>13</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D25" s="1">
+        <v>2024</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="102" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B26" s="1">
+        <v>14</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D26" s="1">
+        <v>2024</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B27" s="1">
+        <v>15</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D27" s="1">
         <v>2023</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E27" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F27" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="136" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B18" s="1">
-        <v>7</v>
-      </c>
-      <c r="C18" s="1" t="s">
+    <row r="28" spans="1:6" ht="136" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B28" s="1">
+        <v>16</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D28" s="1">
         <v>2023</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E28" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F28" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="119" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B19" s="1">
-        <v>8</v>
-      </c>
-      <c r="C19" s="1" t="s">
+    <row r="29" spans="1:6" ht="119" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B29" s="1">
+        <v>17</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D29" s="1">
         <v>2023</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E29" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F29" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="153" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B20" s="1">
-        <v>9</v>
-      </c>
-      <c r="C20" s="1" t="s">
+    <row r="30" spans="1:6" ht="153" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B30" s="1">
+        <v>18</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D30" s="1">
         <v>2023</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E30" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F30" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="153" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B21" s="1">
-        <v>10</v>
-      </c>
-      <c r="C21" s="1" t="s">
+    <row r="31" spans="1:6" ht="153" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B31" s="1">
+        <v>19</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D31" s="1">
         <v>2022</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E31" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F31" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B22" s="1">
-        <v>11</v>
-      </c>
-      <c r="C22" s="1" t="s">
+    <row r="32" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B32" s="1">
+        <v>20</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D32" s="1">
         <v>2022</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E32" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F32" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="153" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B23" s="1">
-        <v>12</v>
-      </c>
-      <c r="C23" s="1" t="s">
+    <row r="33" spans="1:6" ht="153" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B33" s="1">
+        <v>21</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D33" s="1">
         <v>2022</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E33" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F33" s="1" t="s">
         <v>66</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="I5" twoDigitTextYear="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>